--- a/Topic Relevant Comments/Nigeria/Wizarab_Sex Toys and Raping Young Boys.xlsx
+++ b/Topic Relevant Comments/Nigeria/Wizarab_Sex Toys and Raping Young Boys.xlsx
@@ -14,44 +14,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <si>
     <t>text</t>
   </si>
   <si>
-    <t>UNICEF data, clearly reported, 1 in 10 boys suffer sexual violence before 18, and that 2025 study on male undergraduates? 13% reported childhood abuse, with over 54% from female perpetrators, such as maids, aunts, neighbors turning boys into their playthings. Its right there on google. PLOS study even shows higher SV for boys in some spots, mostly by known women. This is highly Underreported because of societal stigma mostly championed by feminists, by gaslighting/dismissing boys pain as "not real abuse."</t>
-  </si>
-  <si>
     <t>The boy child can be abused too and he deserves to be protected just as fiercely. I pray the same energy, urgency and commitment used to identify and punish those who harm girls is also applied when boys are victims.</t>
   </si>
   <si>
     <t>This one is true. The boy child abuse is a serious issue that often gets neglected. Sadly, society expects the boy child to be strong and bottle it all up, while dying in silence. The voice of the boy child matters. More awareness needs to be raised! Protect the boy child!</t>
   </si>
   <si>
-    <t>boys were sexually abvsed by female domestic staffs. I am afraid it hasn't stopped.</t>
-  </si>
-  <si>
     <t>They are less likely to report, less likely to be believed, and in Nigeria, the law does not clearly recognize boys as victims. Child protection must be gender-neutral, loud, and uncompromising. Safeguarding children means safeguarding boys too. No child should be ignored simply because of outdated assumptions about who can and cannot be a victim.</t>
   </si>
   <si>
-    <t>If we start this story, is going to be an unending one. The way society see abusing boys all the way boys or men take it when they are abused also needs to be taken into account.</t>
-  </si>
-  <si>
-    <t>I agree that there are occurrences of boy-child abuse But please can you point me to the link of your statistics? Thank you</t>
-  </si>
-  <si>
-    <t>Yes I was and a lot of young boys out there have been abused to by your horny gender</t>
-  </si>
-  <si>
     <t>Fr man I was saying it the other day. The thing is that People don't like talking about it, but boys have always been victims of sexual abuse too. Just because it's uncomfortable doesn't mean it didn't happen. Older women taking advantage of younger boys is not new</t>
   </si>
   <si>
-    <t>Even with sex toys many are still doing it The male child is being psychologically abused and some men with stds today got it from women who raped them when they were boys</t>
-  </si>
-  <si>
-    <t>Protect the boy child</t>
-  </si>
-  <si>
     <t>Unfortunately true and it's not one sided either. Yes, some women take advantage of young boys. But let's also be honest, some men abuse boys too. I personally know of two different cases where male teachers molested male minors. These things are happening quietly.</t>
   </si>
   <si>
@@ -64,27 +43,15 @@
     <t>This is true Most of my male friends were assaulted at young age and it's so sad because Men voice is not heard enough STOP RAPING OUR BOYS! STOP RAPING OUR GIRLS!</t>
   </si>
   <si>
-    <t>The boy child and the girl child are getting abused. It is high time people started going to jail for s£xual abuse.</t>
-  </si>
-  <si>
     <t>Those boys were either told to enjoy it or silenced thus a statistics flaw. The boy child should also be protected and encouraged to speak out</t>
   </si>
   <si>
-    <t>Boys suffer the most, but no body is ready to talk about the struggles of a boy child.</t>
-  </si>
-  <si>
     <t>This is really disheartening and we are aware it is happening, most parents look away when it comes to the boy child. A boy child's emotional need is not lesser than that of the female child. Parent need to do better to ensure that they are not traumatized emotionally when they grow... We should keep pushing this awareness.... The voice of boy child should not be silenced too....</t>
   </si>
   <si>
-    <t>8 in 10 boys got sexually assaulted by their maid,aunties, and even teachers</t>
-  </si>
-  <si>
     <t>n the painful part is when people downplay the trauma by saying the boys enjoy it too. They are children for God's sakeGod will punish every abuser.</t>
   </si>
   <si>
-    <t>Very bad as no one care about male child wellbeing</t>
-  </si>
-  <si>
     <t>Alot of these boys were molested by close relatives. Stories choke.</t>
   </si>
   <si>
@@ -94,15 +61,9 @@
     <t>Men enjoy it is the reason why they don't report or talk about it. We don't have cases like this reported to station, and no NGO is taking it as a cause for concern. This is what the former PRO said and it got me thinking that, do men get justice for anything at all? Hell No, and we still get backlash for every single thing.</t>
   </si>
   <si>
-    <t>Justice for the boy child, dont be an apologist.</t>
-  </si>
-  <si>
     <t>Don't u think if male Victims felt safe to speak up, we could have clearer data.</t>
   </si>
   <si>
-    <t>Why do you think boys don't speak up about this?</t>
-  </si>
-  <si>
     <t>That claim is serious and shouldn't be thrown around casually. Sexual abuse is wrong regardless of gender, and real discussions need verified facts not harmful generalizations. If you're talking about abuse, it deserves sensitivity and evidence, not statistics without sources.</t>
   </si>
   <si>
@@ -133,27 +94,12 @@
     <t>There was an anonymous thread I came across one certain time on one of this social media platforms where men shared how they were exposed to sex by older women at a very tender age. It was traumatizing reading their experiences, because some of them were exposed to sex as early as 3-7 years old by the so called "older women" some it was their house maids, some it was that big aunty in their neighborhood. While reading, I could only imagine the trauma those boys had to pass through because those horNy predator of women couldn't control their seXual huge. What got me all flared up was the comments being made by some women on the said post. One commented "As if most of them didn't enjoy it", one also said, "Most men are even praying to get raped" I was like wdf Dear HornY sex starved older women, face your dildos and stop mole$ting our young boys.</t>
   </si>
   <si>
-    <t>Many men wey be victims of rape no dey like talk about am</t>
-  </si>
-  <si>
     <t>We've not talked about boys who's earliest memories were sexual and can't fully put the pieces together even as grown adults. They know something sexual happened to them very early, much sooner than they were awake and aware of themselves as a person.</t>
   </si>
   <si>
-    <t>This is 100% facts. I will say this again,most boys that Grew up in the 80s and 90s were all raped by these women you now see making so much noise.</t>
-  </si>
-  <si>
-    <t>Sad truth that women don't want us to talk about. But then who will speak for this young men</t>
-  </si>
-  <si>
-    <t>This is straight up facts They did this on a daily basis If men raped girls as much as women raped boys, society won't be liveable</t>
-  </si>
-  <si>
     <t>Boy child does not have the care or the tender attention girl child commands Gender equality is the key to a very sane society, just look at how Simi saga ended and no single organization or media houses not to talk of child advocacy bodies</t>
   </si>
   <si>
-    <t>Both gender is guilty</t>
-  </si>
-  <si>
     <t>Tf are u expected to say as a guy. Who do u want to prove it to? How do u as a man expected to come out and say you're weak and helpless and u hated yourself that u couldn't do anything about it. Just push on, na Man U be, e no go kpai u</t>
   </si>
   <si>
@@ -175,12 +121,6 @@
     <t>This possibly means that the rapists we have today were taught by women who molested them. It's possible trauma that they're taking out on women.</t>
   </si>
   <si>
-    <t>Some people don't know what boy kids go through. I no wan talk my own part sef</t>
-  </si>
-  <si>
-    <t>Most grown women are rapists, It's the reason they always use tape as a tool because they believe boys don't need to give consent</t>
-  </si>
-  <si>
     <t>I was a victim. My neighbor's daughter fumbled me when I was 10. Still haven't healed from the trauma</t>
   </si>
   <si>
@@ -196,54 +136,33 @@
     <t>This is very true, aunties back then forced young children to massage their thighs and then make them touch their genitals, saying "oya rub that place very well, and do it faster" Most children couldn't speak up cos our parents generation trusts their siblings over their own children. It's sad but it's what a lot of young boys went through growing up.</t>
   </si>
   <si>
-    <t>Even if what you just typed is real but with the advent of sex toys it is now going extinct, so why can't men stop raping women, men, boys, girls and animals even with the advent of male sex toys, soapy etc?</t>
-  </si>
-  <si>
     <t>i dey always try process these stories when boys dey tell me am. because omo growing up nothing like that at all for my ends</t>
   </si>
   <si>
     <t>I was raped by one aunty Mercy at the age of 6, she was from Ugep, whenever my mom left me with her, she will stroke my tiny penis and rub it on her vagina, she always promised to play with me and give me food if I don't tell my mom</t>
   </si>
   <si>
-    <t>Who will even listen to you that a lady rape you How will it makes sense to you if I come out to tell u that a gal did that to me and you believe me without thinking that I go play the dirty first</t>
-  </si>
-  <si>
     <t>I nearly said "you are stupid" before reading everything.... I am a victim, I understand the psychological damage this thing did to me, my mother and father went through hell, to bring my mind to a normal route....Being exposed to sex before you are 6, do you know what that does?</t>
   </si>
   <si>
     <t>The same way it's done to some girls dont make it a gender thing, some girls tell their parents or anyone and they don't still believe them</t>
   </si>
   <si>
-    <t>Yes,the focus is mainly on the female gender most times</t>
-  </si>
-  <si>
-    <t>So now you know it's dangerous. When women claim all of them have been raped or sexually assaulted. We don't hear the statistics. When they say men are rapists, we don't hear statistics. It's now you want to challenge statistics</t>
-  </si>
-  <si>
     <t>Men don't attach emotions to many hints, they could experience terrible things but know how to put it behind them and move forward very quickly. A man would be going through tough times and be smiling and all happy</t>
   </si>
   <si>
-    <t>90% of them have a sex toy right now, this is proof that all you said is true when there was none. They dealt with little boys.</t>
-  </si>
-  <si>
     <t>When I have children, no one would be allowed to refer to them as "my husband" or "my wife". I was a victim of something like this, the experience was far from good. I still live with the scars.</t>
   </si>
   <si>
     <t>This claim is misleading and harmful. Sexual behavior and consent are complex, and spreading such statistics about minors is not accurate and can be dangerous. Where did you get your statistics?</t>
   </si>
   <si>
-    <t>Can you back this up with data... I don't like too much of assumptions. You forgot that time was also more of cavemen days You actually think women were raping boys then? No! I beg to disagree sir Dick</t>
-  </si>
-  <si>
     <t>I remember when faith try and do me this on 31 ist of December 2018 na god help me , if we men talk about what we go through in hand of this girls ,they won't take us serious .</t>
   </si>
   <si>
     <t>Even with the sex toy, they still find a way to take advantage of the young boy. Sex is addictive in nature and not everyone of them found desire in toys. Sometimes human physical touch and body contact make sex more interesting for them, which is why age is never a barrier to them as long as they can feel the touched</t>
   </si>
   <si>
-    <t>I fess dey talk am We too like fuckk for this country As religious as we all are, we too like sex. When you don't see an adult to ease the urge then the boy child pays the price.</t>
-  </si>
-  <si>
     <t>Same with girls thats just the truth , i dont know y it was difficult for boys to speak up more then</t>
   </si>
   <si>
@@ -253,15 +172,6 @@
     <t>If you ever get to sit in uni hostel conversations, the stories guys would tell. Alot of people do not know they were SA. Untold stories are in the millions</t>
   </si>
   <si>
-    <t>Just check online bro. This is the stereotype we talk about. Talk about theft, homicide and shii and we all think a man committed the crime.</t>
-  </si>
-  <si>
-    <t>I no go apologize ke, I no follow ena dey do feminist o I dey bow to men for here.</t>
-  </si>
-  <si>
-    <t>Honestly though This is so real They will never admit it most young guys today lost it due to their aunts cause no proof of being a virgin for guys</t>
-  </si>
-  <si>
     <t>You know these things, same thing was done to me years ago, she kept calling me her husband until she started calling me to come massage her privately and all, I will never forgive her</t>
   </si>
   <si>
@@ -274,15 +184,6 @@
     <t>Is it so hard for you guys to talk without generalization. When you say "women" that includes your mum, sisters, cousins, aunties any female you know. Using "some women" is more appropriate bikonu.</t>
   </si>
   <si>
-    <t>Older cousins, multiple househelps, aunts, neighbors(married &amp; unmarried)... no be everything man eye see e dey talk.</t>
-  </si>
-  <si>
-    <t>There's this girl secondary school that if your ball enter there you will have to beg them to bring it out or forget about it cause if you enter there na gang rape them go do you</t>
-  </si>
-  <si>
-    <t>Ok but just don't moleste little boy wai</t>
-  </si>
-  <si>
     <t>I remember vividly how I experienced stuffs like this. I was brought from the village to come live with my uncle when I was 11 years old. My Uncle's Wife also brought her sister to come and stay with the family. She arrived before I did and had already spent 5 years before I came</t>
   </si>
   <si>
@@ -292,18 +193,6 @@
     <t>They started off with "my husband". Never allow any fool to call your child "my husband".</t>
   </si>
   <si>
-    <t>You will experience this, if you don't your children will! Then we can ask you where you got your statistics. Stupid, nonsensical, fuulish thing</t>
-  </si>
-  <si>
-    <t>I don't think it is a lack of sex toys because currently,not all ladies are with sex toys.</t>
-  </si>
-  <si>
-    <t>Oga he's wrong</t>
-  </si>
-  <si>
-    <t>E get as the thing be bros</t>
-  </si>
-  <si>
     <t>No one dares that shit with my kids. You are not even allowed to use fine boy or fine girl</t>
   </si>
   <si>
@@ -313,66 +202,30 @@
     <t>The fucked up part is I was less than 10yrs old all these events too place... Mom and Dad were bankers working on the island and returned home late.. I'm talking early 2000.. By the time they're back I'm already asleep. This was the routine for many years.</t>
   </si>
   <si>
-    <t>Exactly why they don't take us seriously. Because of this. At that age it wasn't anything fun.</t>
-  </si>
-  <si>
-    <t>The world don't care</t>
-  </si>
-  <si>
     <t>If men start to speak up on this issue,80% of men were molested at a very young age but we're not ready for this discussion</t>
   </si>
   <si>
-    <t>I am a living witness</t>
-  </si>
-  <si>
     <t>Though partly true, the statistics quoted is not supported by credible evidence. Sexual abuse is a serious issue that affects all genders, and it deserves careful, evidence-based discussion ,not sensational statements.</t>
   </si>
   <si>
     <t>I was abused by 2 different woman</t>
   </si>
   <si>
-    <t>I'm a victim</t>
-  </si>
-  <si>
-    <t>Were you abused as a child?</t>
-  </si>
-  <si>
-    <t>I was a victim</t>
-  </si>
-  <si>
     <t>I'm a victim I was raped by our neighbors Daughter back in the days in Aba</t>
   </si>
   <si>
-    <t>but 8 in 10 women have been rap3d by men or s3xually assaulted by men and that is statistically correct?? these women dey muzz me</t>
-  </si>
-  <si>
-    <t>Listen to Advice or be like Samson...</t>
-  </si>
-  <si>
-    <t>We all have our stories, right?</t>
-  </si>
-  <si>
     <t>"" That was the response I got when I shared my ordeal, not once but twice. My painful experiences go back over 20 years, and I was exposed to many sexual situations at a very young age. I hope I get to speak up again in future.</t>
   </si>
   <si>
     <t>We have stories to tell but who is going to believe us</t>
   </si>
   <si>
-    <t>Women can go to extremes when they're h0rny, but society often makes it seem like men are more horny than women.</t>
-  </si>
-  <si>
     <t>and the worst part we were molested by the people our parent would least expect such from</t>
   </si>
   <si>
     <t>I was really victim during my junior secondary school days, and the craziest part is that my molester has a pretty big page right here on X and she posts every.... But that's a story for another day sha</t>
   </si>
   <si>
-    <t>Right. Women go away with a lot in the society, nah when e reach men dem go dey vent muscles</t>
-  </si>
-  <si>
-    <t>All the kids in your family will experience this. Even you will be raped at some point in your life as an adult</t>
-  </si>
-  <si>
     <t>This is 100% true. Had this random conversation with 6 of my friends while in school and found out all of us were sexually assaulted by adult women while still kids. Maid, Cousin, Aunty, Neighbor and all of them go carry innocent face.</t>
   </si>
   <si>
@@ -391,75 +244,27 @@
     <t>I can say that I'm a victim here But thank God my past didnt have a toll on my life Make lying dog just keep on lying sha ‍↕️</t>
   </si>
   <si>
-    <t>How will your d1ck stand when you are not in the mood? Your d1ck need to stand for you to be rap£d.. Someone should educate me please</t>
-  </si>
-  <si>
-    <t>I think men should start getting sex toys also</t>
-  </si>
-  <si>
-    <t>If i share my experience here, everybody go just dey shout "Ahhh "</t>
-  </si>
-  <si>
     <t>This is just the truth. And it's usually the most innocent looking women and indulge in this,those women who pretend to be holy, they are the main perpetrators of this evil act.</t>
   </si>
   <si>
-    <t>It's correct. If a woman posted, you won't say it's misleading. God will judge you</t>
-  </si>
-  <si>
-    <t>If I talk wetin my eyes saw from Aunt Wumi molestation</t>
-  </si>
-  <si>
     <t>This is a delicate topic that we must give attention to</t>
   </si>
   <si>
     <t>I experienced it too</t>
   </si>
   <si>
-    <t>So that means people who cant afford toys still r ape children</t>
-  </si>
-  <si>
     <t>Well he may be not accurate with numbers but you can agree to an extent that this thing happened to many out there</t>
   </si>
   <si>
     <t>The people most likely to prey on kids are those uncles and aunts who are usually entrusted with the kids without scrutiny or second thoughts.</t>
   </si>
   <si>
-    <t>Sorry about your experience</t>
-  </si>
-  <si>
-    <t>Aot of you may disagree but this is absolutely true</t>
-  </si>
-  <si>
-    <t>It's just so sad to think your sexual orientation was programmed (reprogrammed) before you could even realize what life's all about.</t>
-  </si>
-  <si>
     <t>If some house maid confess what they've done to peoples children's People will stop having maid</t>
   </si>
   <si>
-    <t>You're right on this</t>
-  </si>
-  <si>
-    <t>It's high time we start talking about this. It's actually disturbing.</t>
-  </si>
-  <si>
     <t>Reasons why I will try not to have any of my child to stay with so so person cause of condition or employ someone to take care of my kids</t>
   </si>
   <si>
-    <t>It's a sad reality</t>
-  </si>
-  <si>
-    <t>You know difficult people from their comments. They dismiss first, then ask for clarity afterwards. How do you even manage your patients?</t>
-  </si>
-  <si>
-    <t>Better speak up</t>
-  </si>
-  <si>
-    <t>Oh Sorry about your experience</t>
-  </si>
-  <si>
-    <t>This is facts</t>
-  </si>
-  <si>
     <t>Bro I started eating pussy at 7 When I was 9 , our house maid gave me extra meat from the soup if I sucked her breast I went to boarding school (mixed) and senior Sandra and her friends use to call me to female hostel to drink golden morn and they'll tall take turns in me</t>
   </si>
   <si>
@@ -469,30 +274,18 @@
     <t>This is the safest conclusion in the absence of actual facts. May God save the little innocent young children.</t>
   </si>
   <si>
-    <t>Bless. It about all children.</t>
-  </si>
-  <si>
     <t>You're very right. But if we had come out to speak the truth back then, people wouldn't have believed us.. including our own parents. They would have immediately shut us up.</t>
   </si>
   <si>
     <t>Using sex toy sef is a social deformity that most people excuse.</t>
   </si>
   <si>
-    <t>Deep shit. Bitter truth</t>
-  </si>
-  <si>
     <t>Sex toys saved a generation I can relate</t>
   </si>
   <si>
     <t>Hmmm... This is absolutely true. Adult women play with kids peanuts to satisfy their sexual desires. Sex toys have reduced that in this recent years</t>
   </si>
   <si>
-    <t>This is spot on.</t>
-  </si>
-  <si>
-    <t>You need to thank God because if it happened to you there's a chance you could be in prison by now. You may not understand this tweet.</t>
-  </si>
-  <si>
     <t>I lost my virginity to my uncle's fiancee. She used to give me pocket money whenever I was going back to boarding school. I honestly didn't think anything of it until I finished secondary school. She invited me, and that was it. I was 16, she was in her late twenties then.</t>
   </si>
   <si>
@@ -502,118 +295,19 @@
     <t>The funny part is you can't forget it just like that... Till date I've not dated any lady despite being very handsome,Tall, name it .. We just vibe and move on. It changed the way I see women. Worse part is if you have a photographic memory you'd keep remembering every detail</t>
   </si>
   <si>
-    <t>I'm still traumatised even as I'm typing. It it well.</t>
-  </si>
-  <si>
-    <t>This is very true.. What a world</t>
-  </si>
-  <si>
-    <t>Fortunately the world is not ready for this conversation</t>
-  </si>
-  <si>
     <t>Forget social media bro, I had a little bit of experience about it and it wasn't fun</t>
   </si>
   <si>
-    <t>Did you read what was written? How can a 6 years old be enjoying sex, are you okay ni?</t>
-  </si>
-  <si>
-    <t>The statistics need no proof. So true.</t>
-  </si>
-  <si>
-    <t>But till now is still dey happen cause some of the can't afford sex toys</t>
-  </si>
-  <si>
     <t>This!! Happened to me multiple times.</t>
   </si>
   <si>
-    <t>Wow! This is a wild take ... Do u statistics that back up this claim?</t>
-  </si>
-  <si>
-    <t>Unfortunately this is true.</t>
-  </si>
-  <si>
-    <t>Where is the lie?</t>
-  </si>
-  <si>
-    <t>Chai... not a good experience o</t>
-  </si>
-  <si>
-    <t>If I speak ️ Aunty Janet e no go better for you</t>
-  </si>
-  <si>
     <t>Nearly all of us in the comment section were r by our aunties and.</t>
   </si>
   <si>
     <t>My own sup for my yard when I was still in primary 3</t>
   </si>
   <si>
-    <t>Na the new angle be this?</t>
-  </si>
-  <si>
-    <t>We're not ready for this conversation at all. SMH</t>
-  </si>
-  <si>
-    <t>Yes, I was</t>
-  </si>
-  <si>
     <t>Na my landlady house help dealt with me that time. I can't forget it not once not twice.</t>
-  </si>
-  <si>
-    <t>Yeah, I just get flashes anytime this sort of topic is raised.</t>
-  </si>
-  <si>
-    <t>Heal bro.. It's a long time now.. Where is she now?</t>
-  </si>
-  <si>
-    <t>Those kain things, still fresh in the memory till tomorrow</t>
-  </si>
-  <si>
-    <t>Do your own research and bring the data</t>
-  </si>
-  <si>
-    <t>Na that person wey invent the sex toys I wan catch</t>
-  </si>
-  <si>
-    <t>I hope you've gotten over it</t>
-  </si>
-  <si>
-    <t>Omo it is well.. hope you okay gee?</t>
-  </si>
-  <si>
-    <t>I nearly insulted you until I finished reading</t>
-  </si>
-  <si>
-    <t>You're talking of taking it to secondary school, some no carry it to primary school.</t>
-  </si>
-  <si>
-    <t>Now just imagine someone forces you to suck obo where dey smell like rotten flesh</t>
-  </si>
-  <si>
-    <t>E reach my turn dem no Dey rape boys again</t>
-  </si>
-  <si>
-    <t>You are right... But what is boy virginity for crying out loud</t>
-  </si>
-  <si>
-    <t>You're the one with the low IQ. The question you asked last should be what you should have asked firstly.</t>
-  </si>
-  <si>
-    <t>If boys start Dey talk eh</t>
-  </si>
-  <si>
-    <t>Your life don Garnacho</t>
-  </si>
-  <si>
-    <t>Women don really see something for this life wey we come oooo</t>
-  </si>
-  <si>
-    <t>E no dey hard to spot sex starved bitch ass niggas</t>
-  </si>
-  <si>
-    <t>This guy be is my fave og on</t>
-  </si>
-  <si>
-    <t>Ode ni awon family e</t>
   </si>
   <si>
     <t>I could remember what happened in QRC onitsha Anambra many years ago. That 6 girls r a man selling ICE cream to the point the man fainted. The story passed along so many sets then. That school is a bunch of horny girls. If lesbian are 100 in Anambra 70 are from QRC.</t>
@@ -974,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A201"/>
+  <dimension ref="A1:A99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1472,516 +1166,6 @@
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
-      <c r="A100" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1">
-      <c r="A123" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1">
-      <c r="A125" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1">
-      <c r="A131" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1">
-      <c r="A133" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1">
-      <c r="A135" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1">
-      <c r="A136" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1">
-      <c r="A137" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1">
-      <c r="A138" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1">
-      <c r="A140" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1">
-      <c r="A142" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1">
-      <c r="A143" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1">
-      <c r="A144" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1">
-      <c r="A147" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1">
-      <c r="A150" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1">
-      <c r="A153" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1">
-      <c r="A154" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1">
-      <c r="A155" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1">
-      <c r="A156" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1">
-      <c r="A157" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1">
-      <c r="A158" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1">
-      <c r="A159" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1">
-      <c r="A160" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1">
-      <c r="A161" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1">
-      <c r="A162" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1">
-      <c r="A163" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1">
-      <c r="A164" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1">
-      <c r="A165" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1">
-      <c r="A166" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1">
-      <c r="A167" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1">
-      <c r="A168" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1">
-      <c r="A169" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1">
-      <c r="A170" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1">
-      <c r="A171" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1">
-      <c r="A172" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1">
-      <c r="A173" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1">
-      <c r="A174" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1">
-      <c r="A175" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1">
-      <c r="A176" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1">
-      <c r="A177" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1">
-      <c r="A178" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1">
-      <c r="A179" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1">
-      <c r="A180" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1">
-      <c r="A181" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1">
-      <c r="A182" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1">
-      <c r="A183" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1">
-      <c r="A184" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1">
-      <c r="A185" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1">
-      <c r="A186" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1">
-      <c r="A187" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1">
-      <c r="A188" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1">
-      <c r="A189" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1">
-      <c r="A190" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1">
-      <c r="A191" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1">
-      <c r="A192" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1">
-      <c r="A193" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1">
-      <c r="A194" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1">
-      <c r="A195" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1">
-      <c r="A196" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1">
-      <c r="A197" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1">
-      <c r="A198" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1">
-      <c r="A199" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1">
-      <c r="A200" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="201" spans="1:1">
-      <c r="A201" t="s">
-        <v>200</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
